--- a/liteon/dist/20261028_光寶個股模型_v0.2.xlsx
+++ b/liteon/dist/20261028_光寶個股模型_v0.2.xlsx
@@ -7689,26 +7689,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">delta/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台達電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">delta/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台達電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -15760,26 +15760,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">delta/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台達電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">delta/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台達電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -15884,26 +15884,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">delta/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台達電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">delta/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台達電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -16054,26 +16054,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">delta/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台達電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">delta/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台達電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>

--- a/liteon/dist/20261028_光寶個股模型_v0.2.xlsx
+++ b/liteon/dist/20261028_光寶個股模型_v0.2.xlsx
@@ -6920,26 +6920,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7119,26 +7119,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7240,26 +7240,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7361,26 +7361,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7482,26 +7482,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7603,26 +7603,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>

--- a/liteon/dist/20261028_光寶個股模型_v0.2.xlsx
+++ b/liteon/dist/20261028_光寶個股模型_v0.2.xlsx
@@ -6590,7 +6590,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261028_</t>
+      <t xml:space="preserve">tsmc/dist/20261030_</t>
     </r>
     <r>
       <rPr>
@@ -6609,7 +6609,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.xlsx</t>
+      <t xml:space="preserve">_v0.4.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6789,7 +6789,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261028_</t>
+      <t xml:space="preserve">tsmc/dist/20261030_</t>
     </r>
     <r>
       <rPr>
@@ -6808,7 +6808,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.xlsx</t>
+      <t xml:space="preserve">_v0.4.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6910,7 +6910,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261028_</t>
+      <t xml:space="preserve">tsmc/dist/20261030_</t>
     </r>
     <r>
       <rPr>
@@ -6929,7 +6929,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.xlsx</t>
+      <t xml:space="preserve">_v0.4.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7031,7 +7031,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261028_</t>
+      <t xml:space="preserve">tsmc/dist/20261030_</t>
     </r>
     <r>
       <rPr>
@@ -7050,7 +7050,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.xlsx</t>
+      <t xml:space="preserve">_v0.4.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7152,7 +7152,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261028_</t>
+      <t xml:space="preserve">tsmc/dist/20261030_</t>
     </r>
     <r>
       <rPr>
@@ -7171,7 +7171,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.xlsx</t>
+      <t xml:space="preserve">_v0.4.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7273,7 +7273,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261028_</t>
+      <t xml:space="preserve">tsmc/dist/20261030_</t>
     </r>
     <r>
       <rPr>
@@ -7292,7 +7292,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.xlsx</t>
+      <t xml:space="preserve">_v0.4.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7359,7 +7359,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">delta/dist/20261028_</t>
+      <t xml:space="preserve">delta/dist/20261030_</t>
     </r>
     <r>
       <rPr>
@@ -7378,7 +7378,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -15430,7 +15430,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">delta/dist/20261028_</t>
+      <t xml:space="preserve">delta/dist/20261030_</t>
     </r>
     <r>
       <rPr>
@@ -15449,7 +15449,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -15554,7 +15554,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">delta/dist/20261028_</t>
+      <t xml:space="preserve">delta/dist/20261030_</t>
     </r>
     <r>
       <rPr>
@@ -15573,7 +15573,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -15724,7 +15724,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">delta/dist/20261028_</t>
+      <t xml:space="preserve">delta/dist/20261030_</t>
     </r>
     <r>
       <rPr>
@@ -15743,7 +15743,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
